--- a/data/trans_orig/Q5412-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q5412-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11068</t>
+          <t>10151</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>4507</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15245</t>
+          <t>15432</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7127</t>
+          <t>7328</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20203</t>
+          <t>22102</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>281515</t>
+          <t>282432</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>290850</t>
+          <t>290869</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>327689</t>
+          <t>327502</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>339034</t>
+          <t>338427</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>615314</t>
+          <t>613415</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>628390</t>
+          <t>628189</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5589</t>
+          <t>6352</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17494</t>
+          <t>19506</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10837</t>
+          <t>11634</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29500</t>
+          <t>29467</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19739</t>
+          <t>20192</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41866</t>
+          <t>43523</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>192389</t>
+          <t>190377</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>204294</t>
+          <t>203531</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>304408</t>
+          <t>304441</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>323071</t>
+          <t>322274</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>501925</t>
+          <t>500268</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>524052</t>
+          <t>523599</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9797</t>
+          <t>9901</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23707</t>
+          <t>24848</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18336</t>
+          <t>18554</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39283</t>
+          <t>40174</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32339</t>
+          <t>31094</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57103</t>
+          <t>57075</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>478759</t>
+          <t>477618</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>492669</t>
+          <t>492565</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>637559</t>
+          <t>636668</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>658506</t>
+          <t>658288</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1122205</t>
+          <t>1122233</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1146969</t>
+          <t>1148214</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -1992,12 +1992,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18024</t>
+          <t>17190</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2007,12 +2007,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8495</t>
+          <t>7937</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22789</t>
+          <t>21941</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2042,12 +2042,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16047</t>
+          <t>15743</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34727</t>
+          <t>34178</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>291762</t>
+          <t>292596</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>304536</t>
+          <t>304923</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>331207</t>
+          <t>332055</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>345501</t>
+          <t>346059</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>629055</t>
+          <t>629604</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>647735</t>
+          <t>648039</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15213</t>
+          <t>16006</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37400</t>
+          <t>36459</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51022</t>
+          <t>50117</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82339</t>
+          <t>81724</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>69603</t>
+          <t>73265</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>108253</t>
+          <t>112530</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,62%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>212451</t>
+          <t>213392</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>234638</t>
+          <t>233845</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>306640</t>
+          <t>307255</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>337957</t>
+          <t>338862</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>530577</t>
+          <t>526300</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>569227</t>
+          <t>565565</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>88,53%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23922</t>
+          <t>23993</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47916</t>
+          <t>47952</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63076</t>
+          <t>60690</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>96953</t>
+          <t>96024</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>93682</t>
+          <t>94263</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>137367</t>
+          <t>135784</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>511721</t>
+          <t>511685</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>535715</t>
+          <t>535644</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>646022</t>
+          <t>646951</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>679899</t>
+          <t>682285</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1165245</t>
+          <t>1166828</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1208930</t>
+          <t>1208349</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10990</t>
+          <t>11013</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2953</t>
+          <t>2181</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13594</t>
+          <t>12470</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>6156</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19313</t>
+          <t>20826</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>323340</t>
+          <t>323317</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>332364</t>
+          <t>332390</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>364168</t>
+          <t>365292</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>374809</t>
+          <t>375581</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>692779</t>
+          <t>691266</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>706903</t>
+          <t>705936</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -3594,12 +3594,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10823</t>
+          <t>10329</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25876</t>
+          <t>25606</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34345</t>
+          <t>33866</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64428</t>
+          <t>63309</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48857</t>
+          <t>48698</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84214</t>
+          <t>79564</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3679,12 +3679,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,11%</t>
         </is>
       </c>
     </row>
@@ -3707,12 +3707,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>231122</t>
+          <t>231392</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>246175</t>
+          <t>246669</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>335741</t>
+          <t>336860</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>365824</t>
+          <t>366303</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>572953</t>
+          <t>577603</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>608310</t>
+          <t>608469</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,59%</t>
         </is>
       </c>
     </row>
@@ -3937,12 +3937,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14280</t>
+          <t>14012</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32597</t>
+          <t>30937</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39457</t>
+          <t>38867</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72401</t>
+          <t>72647</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59214</t>
+          <t>58349</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>94845</t>
+          <t>95326</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4022,12 +4022,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>558731</t>
+          <t>560391</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>577048</t>
+          <t>577316</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>705530</t>
+          <t>705284</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>738474</t>
+          <t>739064</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1274414</t>
+          <t>1273933</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1310045</t>
+          <t>1310910</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -4505,32 +4505,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6248</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11649</t>
+          <t>11317</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8089</t>
+          <t>8714</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2169</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14655</t>
+          <t>13999</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4575,32 +4575,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>14336</t>
+          <t>15124</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6923</t>
+          <t>10333</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22544</t>
+          <t>21369</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -4618,32 +4618,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>361917</t>
+          <t>400670</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>356516</t>
+          <t>395763</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>365113</t>
+          <t>403890</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4653,32 +4653,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>599518</t>
+          <t>429643</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>592952</t>
+          <t>424358</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>605438</t>
+          <t>433071</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4688,32 +4688,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>961437</t>
+          <t>830312</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>953229</t>
+          <t>824067</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>968850</t>
+          <t>835103</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -4731,17 +4731,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4766,17 +4766,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>607607</t>
+          <t>438357</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>607607</t>
+          <t>438357</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>607607</t>
+          <t>438357</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4801,17 +4801,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>975773</t>
+          <t>845436</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>975773</t>
+          <t>845436</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>975773</t>
+          <t>845436</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4848,32 +4848,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25257</t>
+          <t>27224</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19188</t>
+          <t>19987</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34042</t>
+          <t>35894</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>73693</t>
+          <t>78569</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>63331</t>
+          <t>66167</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>86659</t>
+          <t>90495</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4918,32 +4918,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>98950</t>
+          <t>105793</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86969</t>
+          <t>91923</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>113661</t>
+          <t>122578</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,84%</t>
         </is>
       </c>
     </row>
@@ -4961,32 +4961,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>256756</t>
+          <t>282088</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>247971</t>
+          <t>273418</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>262825</t>
+          <t>289325</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4996,32 +4996,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>352138</t>
+          <t>386040</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>339172</t>
+          <t>374114</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>362500</t>
+          <t>398442</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5031,32 +5031,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>608894</t>
+          <t>668127</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>594183</t>
+          <t>651342</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>620875</t>
+          <t>681997</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>88,12%</t>
         </is>
       </c>
     </row>
@@ -5074,17 +5074,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>282013</t>
+          <t>309312</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>282013</t>
+          <t>309312</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>282013</t>
+          <t>309312</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5109,17 +5109,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5144,17 +5144,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>707844</t>
+          <t>773920</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>707844</t>
+          <t>773920</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>707844</t>
+          <t>773920</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>31505</t>
+          <t>33634</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23719</t>
+          <t>24940</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40976</t>
+          <t>44026</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>81781</t>
+          <t>87283</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40880</t>
+          <t>75369</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>106382</t>
+          <t>100912</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5261,32 +5261,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>113286</t>
+          <t>120918</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>74508</t>
+          <t>106059</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>135928</t>
+          <t>138105</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -5304,32 +5304,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>618673</t>
+          <t>682757</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>609202</t>
+          <t>672365</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>626459</t>
+          <t>691451</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>951657</t>
+          <t>815683</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>927056</t>
+          <t>802054</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>992558</t>
+          <t>827597</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5374,32 +5374,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1570331</t>
+          <t>1498439</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1547689</t>
+          <t>1481252</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1609109</t>
+          <t>1513298</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>93,45%</t>
         </is>
       </c>
     </row>
@@ -5417,17 +5417,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1033438</t>
+          <t>902966</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1033438</t>
+          <t>902966</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1033438</t>
+          <t>902966</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5487,17 +5487,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1683617</t>
+          <t>1619357</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1683617</t>
+          <t>1619357</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1683617</t>
+          <t>1619357</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
